--- a/data/nzd0044/nzd0044.xlsx
+++ b/data/nzd0044/nzd0044.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H540"/>
+  <dimension ref="A1:H545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16638,6 +16638,156 @@
         <v>383.64</v>
       </c>
       <c r="H540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>387.27</v>
+      </c>
+      <c r="C541" t="n">
+        <v>376.27</v>
+      </c>
+      <c r="D541" t="n">
+        <v>376.75</v>
+      </c>
+      <c r="E541" t="n">
+        <v>374.69</v>
+      </c>
+      <c r="F541" t="n">
+        <v>374.64</v>
+      </c>
+      <c r="G541" t="n">
+        <v>381.65</v>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>387.85</v>
+      </c>
+      <c r="C542" t="n">
+        <v>376.86</v>
+      </c>
+      <c r="D542" t="n">
+        <v>377.11</v>
+      </c>
+      <c r="E542" t="n">
+        <v>375.31</v>
+      </c>
+      <c r="F542" t="n">
+        <v>375.74</v>
+      </c>
+      <c r="G542" t="n">
+        <v>382.79</v>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>388.29</v>
+      </c>
+      <c r="C543" t="n">
+        <v>377.27</v>
+      </c>
+      <c r="D543" t="n">
+        <v>377.46</v>
+      </c>
+      <c r="E543" t="n">
+        <v>375.95</v>
+      </c>
+      <c r="F543" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="G543" t="n">
+        <v>384</v>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>388.24</v>
+      </c>
+      <c r="C544" t="n">
+        <v>377.56</v>
+      </c>
+      <c r="D544" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="E544" t="n">
+        <v>376.28</v>
+      </c>
+      <c r="F544" t="n">
+        <v>377.88</v>
+      </c>
+      <c r="G544" t="n">
+        <v>384.91</v>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>388.06</v>
+      </c>
+      <c r="C545" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="D545" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="E545" t="n">
+        <v>376.66</v>
+      </c>
+      <c r="F545" t="n">
+        <v>379.01</v>
+      </c>
+      <c r="G545" t="n">
+        <v>385.61</v>
+      </c>
+      <c r="H545" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16654,7 +16804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B619"/>
+  <dimension ref="A1:B624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22847,6 +22997,56 @@
       </c>
       <c r="B619" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -23015,28 +23215,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06630083730743067</v>
+        <v>-0.05947408441918758</v>
       </c>
       <c r="J2" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="K2" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01405042835757486</v>
+        <v>0.01145490850096254</v>
       </c>
       <c r="M2" t="n">
-        <v>3.528877147965237</v>
+        <v>3.528444421194374</v>
       </c>
       <c r="N2" t="n">
-        <v>19.2595657532797</v>
+        <v>19.23970919618873</v>
       </c>
       <c r="O2" t="n">
-        <v>4.388572177061658</v>
+        <v>4.386309290985843</v>
       </c>
       <c r="P2" t="n">
-        <v>385.5514832048935</v>
+        <v>385.4826416707064</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23093,28 +23293,28 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005776304097469988</v>
+        <v>0.00942191141239662</v>
       </c>
       <c r="J3" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="K3" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001389002693488184</v>
+        <v>0.0003752597049815343</v>
       </c>
       <c r="M3" t="n">
-        <v>3.03806290117782</v>
+        <v>3.028477219572693</v>
       </c>
       <c r="N3" t="n">
-        <v>14.99615804734641</v>
+        <v>14.90463038428726</v>
       </c>
       <c r="O3" t="n">
-        <v>3.872487320488785</v>
+        <v>3.860651549193123</v>
       </c>
       <c r="P3" t="n">
-        <v>374.6644184462832</v>
+        <v>374.6276530749764</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23171,28 +23371,28 @@
         <v>0.1222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09504717876386314</v>
+        <v>-0.09273398112171216</v>
       </c>
       <c r="J4" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="K4" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05090712807440123</v>
+        <v>0.04936245675443096</v>
       </c>
       <c r="M4" t="n">
-        <v>2.689356569681789</v>
+        <v>2.675635700848584</v>
       </c>
       <c r="N4" t="n">
-        <v>10.51603208271301</v>
+        <v>10.43840442003318</v>
       </c>
       <c r="O4" t="n">
-        <v>3.242843209702407</v>
+        <v>3.230851965044697</v>
       </c>
       <c r="P4" t="n">
-        <v>378.4665071084493</v>
+        <v>378.4431776538545</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23249,28 +23449,28 @@
         <v>0.1361</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1758797675792972</v>
+        <v>-0.1797163022316999</v>
       </c>
       <c r="J5" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="K5" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1500233754650283</v>
+        <v>0.1574200763375605</v>
       </c>
       <c r="M5" t="n">
-        <v>2.580165539757823</v>
+        <v>2.579297461184278</v>
       </c>
       <c r="N5" t="n">
-        <v>10.94266597094712</v>
+        <v>10.89592362953334</v>
       </c>
       <c r="O5" t="n">
-        <v>3.307970068024667</v>
+        <v>3.300897397607708</v>
       </c>
       <c r="P5" t="n">
-        <v>382.861318284654</v>
+        <v>382.8999955844865</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23327,28 +23527,28 @@
         <v>0.1034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1493838465189149</v>
+        <v>-0.1605044727108121</v>
       </c>
       <c r="J6" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="K6" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04783751737048625</v>
+        <v>0.05497171867473072</v>
       </c>
       <c r="M6" t="n">
-        <v>4.348213335034433</v>
+        <v>4.37555425338057</v>
       </c>
       <c r="N6" t="n">
-        <v>27.73275628871651</v>
+        <v>27.91373060391253</v>
       </c>
       <c r="O6" t="n">
-        <v>5.266189921443823</v>
+        <v>5.283344641788243</v>
       </c>
       <c r="P6" t="n">
-        <v>387.6466225870024</v>
+        <v>387.7587389911911</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23405,28 +23605,28 @@
         <v>0.1285</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2509769528407503</v>
+        <v>-0.2630545601913421</v>
       </c>
       <c r="J7" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="K7" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1038415755045347</v>
+        <v>0.1132911861766341</v>
       </c>
       <c r="M7" t="n">
-        <v>4.681191318020775</v>
+        <v>4.708924867699477</v>
       </c>
       <c r="N7" t="n">
-        <v>33.94099222084363</v>
+        <v>34.13616156026728</v>
       </c>
       <c r="O7" t="n">
-        <v>5.825889822236912</v>
+        <v>5.842615986034619</v>
       </c>
       <c r="P7" t="n">
-        <v>397.9388813908228</v>
+        <v>398.0606492881579</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23464,7 +23664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H540"/>
+  <dimension ref="A1:H545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46147,6 +46347,216 @@
         </is>
       </c>
     </row>
+    <row r="541">
+      <c r="A541" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>-35.00164470878399,173.791345548405</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>-35.00184775197254,173.7922156884155</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>-35.00192336804265,173.7930983334033</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-35.001948019589875,173.79397976677774</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-35.001868313528476,173.7948529295936</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-35.001591022829075,173.79565348410134</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>-35.001639528967175,173.79134642484127</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>-35.00184247130024,173.79221647257327</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>-35.00192012667337,173.79309854559548</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-35.001942438498084,173.79397937382066</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-35.00185862673056,173.7948503391448</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>-35.00158125572602,173.79564959021562</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>-35.001635599450985,173.7913470897239</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>-35.00183880168051,173.7922170174964</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>-35.00191697534213,173.79309875189347</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-35.001936677371084,173.7939789681876</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-35.00184902799436,173.79484777224616</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>-35.00157088888844,173.79564545723267</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>-35.00163604598691,173.79134701416905</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>-35.001836206095824,173.79221740292982</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>-35.00191526461945,173.7930988638838</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-35.001933706789984,173.79397875903308</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>-35.00183978150529,173.79484529954624</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-35.00156309234104,173.79564234895696</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>-35.001637653516255,173.7913467421716</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>-35.001838622674676,173.792217044078</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>-35.00191526461945,173.7930988638838</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-35.00193028612081,173.79397851818848</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-35.00182983052174,173.79484263845077</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-35.001557094996826,173.79563995797602</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0044/nzd0044.xlsx
+++ b/data/nzd0044/nzd0044.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H545"/>
+  <dimension ref="A1:H548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16790,6 +16790,96 @@
       <c r="H545" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="C546" t="n">
+        <v>377.52</v>
+      </c>
+      <c r="D546" t="n">
+        <v>378.23</v>
+      </c>
+      <c r="E546" t="n">
+        <v>377.59</v>
+      </c>
+      <c r="F546" t="n">
+        <v>380.09</v>
+      </c>
+      <c r="G546" t="n">
+        <v>387.13</v>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>388.22</v>
+      </c>
+      <c r="C547" t="n">
+        <v>377.73</v>
+      </c>
+      <c r="D547" t="n">
+        <v>378.6</v>
+      </c>
+      <c r="E547" t="n">
+        <v>378.16</v>
+      </c>
+      <c r="F547" t="n">
+        <v>381.42</v>
+      </c>
+      <c r="G547" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>388.13</v>
+      </c>
+      <c r="C548" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="D548" t="n">
+        <v>378.9</v>
+      </c>
+      <c r="E548" t="n">
+        <v>378.74</v>
+      </c>
+      <c r="F548" t="n">
+        <v>382</v>
+      </c>
+      <c r="G548" t="n">
+        <v>388.98</v>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16804,7 +16894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B624"/>
+  <dimension ref="A1:B627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23047,6 +23137,36 @@
       </c>
       <c r="B624" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23215,28 +23335,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05947408441918758</v>
+        <v>-0.05533134472715949</v>
       </c>
       <c r="J2" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K2" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01145490850096254</v>
+        <v>0.009987778001104952</v>
       </c>
       <c r="M2" t="n">
-        <v>3.528444421194374</v>
+        <v>3.528699915184617</v>
       </c>
       <c r="N2" t="n">
-        <v>19.23970919618873</v>
+        <v>19.23260260346841</v>
       </c>
       <c r="O2" t="n">
-        <v>4.386309290985843</v>
+        <v>4.385499128202902</v>
       </c>
       <c r="P2" t="n">
-        <v>385.4826416707064</v>
+        <v>385.4407386415504</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23293,28 +23413,28 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00942191141239662</v>
+        <v>0.01213396192531403</v>
       </c>
       <c r="J3" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K3" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003752597049815343</v>
+        <v>0.0006273185794932745</v>
       </c>
       <c r="M3" t="n">
-        <v>3.028477219572693</v>
+        <v>3.025438959293361</v>
       </c>
       <c r="N3" t="n">
-        <v>14.90463038428726</v>
+        <v>14.86512314432606</v>
       </c>
       <c r="O3" t="n">
-        <v>3.860651549193123</v>
+        <v>3.855531499589396</v>
       </c>
       <c r="P3" t="n">
-        <v>374.6276530749764</v>
+        <v>374.6002203366313</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23371,28 +23491,28 @@
         <v>0.1222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09273398112171216</v>
+        <v>-0.09017815822334874</v>
       </c>
       <c r="J4" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K4" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04936245675443096</v>
+        <v>0.0471337402780625</v>
       </c>
       <c r="M4" t="n">
-        <v>2.675635700848584</v>
+        <v>2.67302601873992</v>
       </c>
       <c r="N4" t="n">
-        <v>10.43840442003318</v>
+        <v>10.41901586938916</v>
       </c>
       <c r="O4" t="n">
-        <v>3.230851965044697</v>
+        <v>3.227850038243592</v>
       </c>
       <c r="P4" t="n">
-        <v>378.4431776538545</v>
+        <v>378.4173235536942</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23449,28 +23569,28 @@
         <v>0.1361</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1797163022316999</v>
+        <v>-0.1796088487616451</v>
       </c>
       <c r="J5" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K5" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1574200763375605</v>
+        <v>0.1587078342392245</v>
       </c>
       <c r="M5" t="n">
-        <v>2.579297461184278</v>
+        <v>2.567430557327863</v>
       </c>
       <c r="N5" t="n">
-        <v>10.89592362953334</v>
+        <v>10.83746905233109</v>
       </c>
       <c r="O5" t="n">
-        <v>3.300897397607708</v>
+        <v>3.292031143888389</v>
       </c>
       <c r="P5" t="n">
-        <v>382.8999955844865</v>
+        <v>382.8989045322907</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23527,28 +23647,28 @@
         <v>0.1034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1605044727108121</v>
+        <v>-0.1626919192516124</v>
       </c>
       <c r="J6" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K6" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05497171867473072</v>
+        <v>0.05692313379792457</v>
       </c>
       <c r="M6" t="n">
-        <v>4.37555425338057</v>
+        <v>4.364771449756857</v>
       </c>
       <c r="N6" t="n">
-        <v>27.91373060391253</v>
+        <v>27.79164078500477</v>
       </c>
       <c r="O6" t="n">
-        <v>5.283344641788243</v>
+        <v>5.271777763241236</v>
       </c>
       <c r="P6" t="n">
-        <v>387.7587389911911</v>
+        <v>387.7808585876718</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23605,28 +23725,28 @@
         <v>0.1285</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2630545601913421</v>
+        <v>-0.2657317168520865</v>
       </c>
       <c r="J7" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K7" t="n">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1132911861766341</v>
+        <v>0.116333316377768</v>
       </c>
       <c r="M7" t="n">
-        <v>4.708924867699477</v>
+        <v>4.69864991102226</v>
       </c>
       <c r="N7" t="n">
-        <v>34.13616156026728</v>
+        <v>33.99343812694899</v>
       </c>
       <c r="O7" t="n">
-        <v>5.842615986034619</v>
+        <v>5.830389191722023</v>
       </c>
       <c r="P7" t="n">
-        <v>398.0606492881579</v>
+        <v>398.087722591734</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23664,7 +23784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H545"/>
+  <dimension ref="A1:H548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46557,6 +46677,132 @@
         </is>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>-35.00163729628753,173.79134680261546</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>-35.00183656410751,173.7922173497666</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>-35.001910042413385,173.79309920574897</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-35.0019219144831,173.79397792875318</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>-35.00182031984711,173.7948400951035</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-35.00154407219203,173.795634766133</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>-35.001636224601285,173.7913469839471</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>-35.00183468454618,173.79221762887352</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>-35.00190671100607,173.79309942383537</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-35.00191678347933,173.79397756748645</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-35.00180860762734,173.7948369630193</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-35.00153233453222,173.7956300866443</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-35.00163702836595,173.79134684794838</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-35.00183423703157,173.79221769532754</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-35.00190400986501,173.79309960066215</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-35.001911562457956,173.79397719988177</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-35.00180350004274,173.79483559714825</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-35.00152822206743,173.79562844711575</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0044/nzd0044.xlsx
+++ b/data/nzd0044/nzd0044.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H548"/>
+  <dimension ref="A1:H550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16880,6 +16880,66 @@
       <c r="H548" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>387.52</v>
+      </c>
+      <c r="C549" t="n">
+        <v>377.58</v>
+      </c>
+      <c r="D549" t="n">
+        <v>379.13</v>
+      </c>
+      <c r="E549" t="n">
+        <v>378.95</v>
+      </c>
+      <c r="F549" t="n">
+        <v>382.39</v>
+      </c>
+      <c r="G549" t="n">
+        <v>389.53</v>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>387.37</v>
+      </c>
+      <c r="C550" t="n">
+        <v>377.24</v>
+      </c>
+      <c r="D550" t="n">
+        <v>378.96</v>
+      </c>
+      <c r="E550" t="n">
+        <v>378.89</v>
+      </c>
+      <c r="F550" t="n">
+        <v>382.53</v>
+      </c>
+      <c r="G550" t="n">
+        <v>389.73</v>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16894,7 +16954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23167,6 +23227,26 @@
       </c>
       <c r="B627" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -23335,28 +23415,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05533134472715949</v>
+        <v>-0.05307623948622615</v>
       </c>
       <c r="J2" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K2" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009987778001104952</v>
+        <v>0.009243112950504062</v>
       </c>
       <c r="M2" t="n">
-        <v>3.528699915184617</v>
+        <v>3.526681023653616</v>
       </c>
       <c r="N2" t="n">
-        <v>19.23260260346841</v>
+        <v>19.20676773926245</v>
       </c>
       <c r="O2" t="n">
-        <v>4.385499128202902</v>
+        <v>4.382552651054229</v>
       </c>
       <c r="P2" t="n">
-        <v>385.4407386415504</v>
+        <v>385.4178456223904</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23413,28 +23493,28 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01213396192531403</v>
+        <v>0.01373316760978358</v>
       </c>
       <c r="J3" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K3" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006273185794932745</v>
+        <v>0.0008080857284633591</v>
       </c>
       <c r="M3" t="n">
-        <v>3.025438959293361</v>
+        <v>3.022342458599244</v>
       </c>
       <c r="N3" t="n">
-        <v>14.86512314432606</v>
+        <v>14.83330989633421</v>
       </c>
       <c r="O3" t="n">
-        <v>3.855531499589396</v>
+        <v>3.851403626774817</v>
       </c>
       <c r="P3" t="n">
-        <v>374.6002203366313</v>
+        <v>374.5839858266441</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23491,28 +23571,28 @@
         <v>0.1222</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09017815822334874</v>
+        <v>-0.08820441538143026</v>
       </c>
       <c r="J4" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K4" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0471337402780625</v>
+        <v>0.04535951460593657</v>
       </c>
       <c r="M4" t="n">
-        <v>2.67302601873992</v>
+        <v>2.67257610988051</v>
       </c>
       <c r="N4" t="n">
-        <v>10.41901586938916</v>
+        <v>10.41495160769853</v>
       </c>
       <c r="O4" t="n">
-        <v>3.227850038243592</v>
+        <v>3.227220415109345</v>
       </c>
       <c r="P4" t="n">
-        <v>378.4173235536942</v>
+        <v>378.3972868332848</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23569,28 +23649,28 @@
         <v>0.1361</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1796088487616451</v>
+        <v>-0.1790430557193307</v>
       </c>
       <c r="J5" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K5" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1587078342392245</v>
+        <v>0.1588042967570136</v>
       </c>
       <c r="M5" t="n">
-        <v>2.567430557327863</v>
+        <v>2.561043204258638</v>
       </c>
       <c r="N5" t="n">
-        <v>10.83746905233109</v>
+        <v>10.8007748810814</v>
       </c>
       <c r="O5" t="n">
-        <v>3.292031143888389</v>
+        <v>3.286453237318522</v>
       </c>
       <c r="P5" t="n">
-        <v>382.8989045322907</v>
+        <v>382.8931608101144</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23647,28 +23727,28 @@
         <v>0.1034</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1626919192516124</v>
+        <v>-0.1632824491601292</v>
       </c>
       <c r="J6" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K6" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05692313379792457</v>
+        <v>0.05770257444010773</v>
       </c>
       <c r="M6" t="n">
-        <v>4.364771449756857</v>
+        <v>4.35240217437897</v>
       </c>
       <c r="N6" t="n">
-        <v>27.79164078500477</v>
+        <v>27.6934448143429</v>
       </c>
       <c r="O6" t="n">
-        <v>5.271777763241236</v>
+        <v>5.262456157949718</v>
       </c>
       <c r="P6" t="n">
-        <v>387.7808585876718</v>
+        <v>387.7868534138975</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23725,28 +23805,28 @@
         <v>0.1285</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2657317168520865</v>
+        <v>-0.2665489408199593</v>
       </c>
       <c r="J7" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K7" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L7" t="n">
-        <v>0.116333316377768</v>
+        <v>0.1177033266985039</v>
       </c>
       <c r="M7" t="n">
-        <v>4.69864991102226</v>
+        <v>4.686230941286078</v>
       </c>
       <c r="N7" t="n">
-        <v>33.99343812694899</v>
+        <v>33.87544282747019</v>
       </c>
       <c r="O7" t="n">
-        <v>5.830389191722023</v>
+        <v>5.820261405424175</v>
       </c>
       <c r="P7" t="n">
-        <v>398.087722591734</v>
+        <v>398.096018724052</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23784,7 +23864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H548"/>
+  <dimension ref="A1:H550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46803,6 +46883,90 @@
         </is>
       </c>
     </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-35.00164247610433,173.79134592617925</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-35.00183602708998,173.7922174295114</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-35.001901938990166,173.79309973622935</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-35.001909672088146,173.79397706678353</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>-35.00180006563239,173.79483467871785</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>-35.00152350986814,173.7956265684895</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-35.00164381571212,173.7913456995147</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-35.00183907018928,173.79221697762398</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-35.00190346963679,173.7930996360275</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-35.001910212193806,173.7939771048116</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-35.001798832767136,173.7948343490249</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-35.001521796341116,173.79562588535273</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
